--- a/data/trans_dic/P37A$medicootras-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P37A$medicootras-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,44%</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,12</t>
+          <t>0,0; 2,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,71</t>
+          <t>0,0; 1,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,69</t>
+          <t>0,0; 1,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,27</t>
+          <t>0,0; 1,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -742,37 +742,37 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,07; 5,86</t>
+          <t>1,1; 5,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,35</t>
+          <t>0,31; 3,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,06; 1,96</t>
+          <t>0,15; 1,64</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,78</t>
+          <t>0,0; 1,52</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,72; 3,2</t>
+          <t>0,69; 3,2</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,74</t>
+          <t>0,27; 2,04</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,89</t>
+          <t>0,13; 1,12</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -857,27 +857,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,05</t>
+          <t>0,0; 1,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,31</t>
+          <t>0,0; 2,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,95</t>
+          <t>0,21; 1,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,8</t>
+          <t>0,44; 3,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,75</t>
+          <t>0,19; 1,79</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -887,32 +887,32 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,22</t>
+          <t>0,0; 1,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,84</t>
+          <t>0,47; 1,75</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,01</t>
+          <t>0,1; 1,02</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,36</t>
+          <t>0,1; 1,24</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,12</t>
+          <t>0,2; 1,14</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,23</t>
+          <t>0,59; 2,23</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,39</t>
+          <t>0,0; 1,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,47</t>
+          <t>0,0; 1,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,62</t>
+          <t>0,34; 2,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,37 +1022,37 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,22</t>
+          <t>0,0; 2,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,28</t>
+          <t>0,52; 3,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,75</t>
+          <t>0,32; 1,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,74</t>
+          <t>0,0; 0,69</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,26</t>
+          <t>0,14; 1,38</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,62</t>
+          <t>0,28; 1,55</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,68</t>
+          <t>0,44; 1,67</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,41</t>
+          <t>0,0; 1,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,83</t>
+          <t>0,0; 2,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,6</t>
+          <t>0,48; 2,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,77</t>
+          <t>0,23; 2,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1162,37 +1162,37 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,11</t>
+          <t>0,0; 1,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,76; 3,67</t>
+          <t>0,79; 3,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,33</t>
+          <t>0,41; 3,24</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,64</t>
+          <t>0,0; 0,59</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,48</t>
+          <t>0,15; 1,44</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,65</t>
+          <t>0,83; 2,62</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,83</t>
+          <t>0,44; 2,14</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,18%</t>
         </is>
       </c>
     </row>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,88</t>
+          <t>0,0; 2,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,73</t>
+          <t>0,0; 1,19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,42</t>
+          <t>0,0; 1,26</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,46</t>
+          <t>0,0; 0,65</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,33</t>
+          <t>0,0; 2,7</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1437,42 +1437,42 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,64</t>
+          <t>0,0; 2,6</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,38</t>
+          <t>0,35; 3,42</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,52</t>
+          <t>0,0; 2,34</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,87</t>
+          <t>0,39; 2,78</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,33</t>
+          <t>0,0; 1,43</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,34</t>
+          <t>0,37; 2,23</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,24</t>
+          <t>0,0; 1,17</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,52</t>
+          <t>0,23; 1,35</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -1557,27 +1557,27 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,79</t>
+          <t>0,0; 0,77</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,11</t>
+          <t>0,0; 1,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,64</t>
+          <t>0,5; 2,77</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,98</t>
+          <t>0,45; 2,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,92</t>
+          <t>0,0; 0,93</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1592,27 +1592,27 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,86; 3,38</t>
+          <t>1,69; 3,82</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,62</t>
+          <t>0,08; 0,69</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,91</t>
+          <t>0,15; 0,98</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,71</t>
+          <t>0,43; 1,59</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,37</t>
+          <t>1,26; 2,66</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -1697,12 +1697,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,84</t>
+          <t>0,0; 0,97</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,79</t>
+          <t>0,14; 1,7</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,81</t>
+          <t>0,0; 0,89</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,01</t>
+          <t>0,12; 1,13</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1732,27 +1732,27 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,06</t>
+          <t>0,72; 2,1</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,42</t>
+          <t>0,0; 0,45</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,08</t>
+          <t>0,24; 1,07</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,5</t>
+          <t>0,06; 0,48</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,06</t>
+          <t>0,44; 1,2</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,44</t>
+          <t>0,09; 0,45</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,82</t>
+          <t>0,29; 0,81</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,36; 0,95</t>
+          <t>0,37; 0,94</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,36; 0,95</t>
+          <t>0,41; 1,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,45</t>
+          <t>0,1; 0,43</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,12</t>
+          <t>0,48; 1,08</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,39; 0,97</t>
+          <t>0,41; 0,98</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,86; 1,52</t>
+          <t>1,02; 1,7</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,37</t>
+          <t>0,13; 0,38</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0,43; 0,84</t>
+          <t>0,45; 0,85</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,44; 0,84</t>
+          <t>0,46; 0,85</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,69; 1,13</t>
+          <t>0,8; 1,24</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>857</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t>1913</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1797</t>
+          <t>2769</t>
         </is>
       </c>
     </row>
@@ -2209,22 +2209,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 8521</t>
+          <t>0; 7551</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 5030</t>
+          <t>0; 5585</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4963</t>
+          <t>0; 5136</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 849</t>
+          <t>0; 4103</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2234,37 +2234,37 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3080; 16846</t>
+          <t>3158; 16767</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>888; 9669</t>
+          <t>884; 9572</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>172; 5676</t>
+          <t>479; 5190</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 9498</t>
+          <t>0; 8109</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4204; 18614</t>
+          <t>3993; 18605</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1568; 10123</t>
+          <t>1558; 11855</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>337; 5377</t>
+          <t>840; 7110</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7016</t>
+          <t>7040</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5070</t>
+          <t>5153</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>12086</t>
+          <t>12192</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5199</t>
+          <t>0; 5879</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 11688</t>
+          <t>0; 10780</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1050; 9798</t>
+          <t>1046; 9484</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2096; 19721</t>
+          <t>2339; 17367</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>957; 8828</t>
+          <t>960; 9040</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 6959</t>
+          <t>0; 6987</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 6385</t>
+          <t>0; 5458</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2386; 9475</t>
+          <t>2558; 9550</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1054; 10062</t>
+          <t>1047; 10163</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1786; 13954</t>
+          <t>1007; 12765</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2063; 11456</t>
+          <t>2064; 11696</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6039; 22998</t>
+          <t>6326; 24005</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3287</t>
+          <t>3183</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2851</t>
+          <t>2908</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6138</t>
+          <t>6091</t>
         </is>
       </c>
     </row>
@@ -2625,12 +2625,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4447</t>
+          <t>0; 4208</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4761</t>
+          <t>0; 4718</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2640,7 +2640,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1067; 8291</t>
+          <t>1074; 8031</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2650,37 +2650,37 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 7560</t>
+          <t>0; 7525</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1782; 11017</t>
+          <t>1745; 10756</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1039; 6118</t>
+          <t>1123; 6594</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 4844</t>
+          <t>0; 4506</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>939; 8353</t>
+          <t>935; 9208</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1754; 10587</t>
+          <t>1816; 10157</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2727; 11203</t>
+          <t>2929; 11247</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3113</t>
+          <t>3146</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>4165</t>
+          <t>5142</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>7278</t>
+          <t>8288</t>
         </is>
       </c>
     </row>
@@ -2833,22 +2833,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 5071</t>
+          <t>0; 4267</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 6853</t>
+          <t>0; 7859</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1774; 9602</t>
+          <t>1762; 10453</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>836; 8670</t>
+          <t>849; 8770</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2858,37 +2858,37 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 8223</t>
+          <t>0; 7757</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2961; 14198</t>
+          <t>3052; 14366</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1090; 11099</t>
+          <t>1744; 13677</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 4661</t>
+          <t>0; 4290</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1140; 11321</t>
+          <t>1136; 10968</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6053; 20100</t>
+          <t>6258; 19853</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2903; 14432</t>
+          <t>3518; 16997</t>
         </is>
       </c>
     </row>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>791</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>791</t>
         </is>
       </c>
     </row>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 6327</t>
+          <t>0; 6294</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 1886</t>
+          <t>0; 2722</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 6130</t>
+          <t>0; 5428</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 2011</t>
+          <t>0; 2830</t>
         </is>
       </c>
     </row>
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>3275</t>
+          <t>3292</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>3275</t>
+          <t>3292</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 6394</t>
+          <t>0; 7407</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -3269,42 +3269,42 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 7333</t>
+          <t>0; 7221</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>978; 9456</t>
+          <t>980; 9575</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 6893</t>
+          <t>0; 6381</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>988; 7385</t>
+          <t>1038; 7321</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 7316</t>
+          <t>0; 7871</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2126; 12962</t>
+          <t>2046; 12371</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 6663</t>
+          <t>0; 6289</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1257; 8030</t>
+          <t>1210; 7223</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6056</t>
+          <t>7553</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>17464</t>
+          <t>19828</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>23520</t>
+          <t>27381</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 4887</t>
+          <t>0; 4744</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 7378</t>
+          <t>0; 7493</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3334; 17352</t>
+          <t>3260; 18154</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2780; 12378</t>
+          <t>3250; 14381</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 5898</t>
+          <t>0; 5916</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>942; 8352</t>
+          <t>948; 8345</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1639; 11869</t>
+          <t>1691; 11876</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>7305; 28733</t>
+          <t>13037; 29465</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>947; 7827</t>
+          <t>952; 8587</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1995; 12402</t>
+          <t>2086; 13357</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6343; 23105</t>
+          <t>5862; 21496</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>14255; 34911</t>
+          <t>18848; 39717</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1079</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>8822</t>
+          <t>10255</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>9901</t>
+          <t>11519</t>
         </is>
       </c>
     </row>
@@ -3665,22 +3665,22 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 6271</t>
+          <t>0; 7231</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1861; 13917</t>
+          <t>1056; 13267</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>907; 7749</t>
+          <t>917; 7800</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 7563</t>
+          <t>0; 7129</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>965; 8291</t>
+          <t>963; 9282</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -3700,27 +3700,27 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>4776; 14810</t>
+          <t>5958; 17468</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0; 6468</t>
+          <t>0; 6908</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3992; 17246</t>
+          <t>3923; 17204</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>917; 8054</t>
+          <t>918; 7733</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>5148; 17473</t>
+          <t>7209; 19486</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>20716</t>
+          <t>23043</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>43800</t>
+          <t>49281</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>64516</t>
+          <t>72324</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2907; 14457</t>
+          <t>2979; 14692</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>9266; 28163</t>
+          <t>9776; 27767</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>12383; 32105</t>
+          <t>12605; 31835</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>12427; 32778</t>
+          <t>14427; 35185</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>3235; 15080</t>
+          <t>3238; 14612</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>17003; 39836</t>
+          <t>17138; 38382</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>13900; 34501</t>
+          <t>14526; 34650</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>32107; 56453</t>
+          <t>38129; 63449</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>8652; 24923</t>
+          <t>8863; 25425</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>30317; 58695</t>
+          <t>31271; 59397</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>30556; 58271</t>
+          <t>31829; 58698</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>49790; 80917</t>
+          <t>57944; 89819</t>
         </is>
       </c>
     </row>
